--- a/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Jefe de Cocina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sous Chef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Jefe de Sala" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Camarero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Barman" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jefe de Cocina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sous Chef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jefe de Sala" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camarero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barman" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Jefe de Cocina'!$A$1:$G$31</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Sous Chef'!$A$1:$G$27</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Jefe de Sala'!$A$1:$G$30</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Camarero'!$A$1:$G$32</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Barman'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Jefe de Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Jefe de Cocina'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sous Chef'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Sous Chef'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jefe de Sala'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jefe de Sala'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Barman'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Barman'!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -133,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -155,58 +160,117 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -566,15 +630,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -582,6 +647,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -589,9 +655,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -613,9 +677,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -623,8 +685,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -633,18 +720,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -661,10 +748,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -689,7 +777,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -704,18 +792,16 @@
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -741,10 +827,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -770,10 +854,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -799,10 +881,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -828,10 +908,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -857,10 +935,8 @@
       <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="26" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -885,24 +961,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="8" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="25" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="26" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -928,10 +1003,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="26" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -957,10 +1030,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="26" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -986,10 +1057,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="26" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1014,24 +1083,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1057,10 +1125,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="26" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1086,10 +1152,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="26" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1115,10 +1179,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="26" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1144,10 +1206,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="26" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1172,6 +1232,8 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="8" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
@@ -1180,17 +1242,19 @@
       </c>
       <c r="D27" s="15">
         <f>COUNTIF(F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n">
-        <v>15</v>
-      </c>
-    </row>
+      <c r="F27" s="15">
+        <f>COUNTIF(B5:B25,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -1198,13 +1262,17 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="25" t="n"/>
       <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F29" s="8" t="n"/>
-    </row>
+      <c r="G29" s="25" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
@@ -1216,20 +1284,33 @@
   <mergeCells count="8">
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1238,18 +1319,18 @@
   <sheetPr>
     <tabColor rgb="00388E3C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1266,10 +1347,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1294,7 +1376,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1309,18 +1391,16 @@
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1346,10 +1426,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1375,10 +1453,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1404,10 +1480,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1433,10 +1507,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1461,24 +1533,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="8" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="26" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1504,10 +1575,8 @@
       <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="26" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1533,10 +1602,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="26" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1561,24 +1628,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="26" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1604,10 +1670,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="26" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1633,10 +1697,8 @@
       <c r="G19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1661,6 +1723,8 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="8" t="n"/>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
@@ -1669,17 +1733,19 @@
       </c>
       <c r="D23" s="15">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n">
-        <v>11</v>
-      </c>
-    </row>
+      <c r="F23" s="15">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
@@ -1687,13 +1753,17 @@
         </is>
       </c>
       <c r="B25" s="8" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="25" t="n"/>
       <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
-    </row>
+      <c r="G25" s="25" t="n"/>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
@@ -1712,13 +1782,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B25:D25"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1727,18 +1810,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1755,10 +1838,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1783,7 +1867,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1798,18 +1882,16 @@
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1835,10 +1917,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1864,10 +1944,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1893,10 +1971,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1922,10 +1998,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1950,24 +2024,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="8" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="26" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1993,10 +2066,8 @@
       <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="26" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2022,10 +2093,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="26" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2051,10 +2120,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="26" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2080,10 +2147,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="26" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2108,24 +2173,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="8" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="19" t="n"/>
-      <c r="G19" s="19" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="25" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2151,10 +2215,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="26" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2180,10 +2242,8 @@
       <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="26" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2209,10 +2269,8 @@
       <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="26" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2237,6 +2295,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="8" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
@@ -2245,17 +2305,19 @@
       </c>
       <c r="D26" s="15">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="15" t="n">
-        <v>14</v>
-      </c>
-    </row>
+      <c r="F26" s="15">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
@@ -2263,13 +2325,17 @@
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="25" t="n"/>
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
-    </row>
+      <c r="G28" s="25" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
@@ -2288,13 +2354,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G24">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2303,18 +2382,18 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2331,10 +2410,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2359,7 +2439,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2374,18 +2454,16 @@
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2411,10 +2489,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2440,10 +2516,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2469,10 +2543,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2498,10 +2570,8 @@
       <c r="G9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2526,24 +2596,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="8" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="26" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2569,10 +2638,8 @@
       <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="26" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2598,10 +2665,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="26" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2627,10 +2692,8 @@
       <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="26" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2656,10 +2719,8 @@
       <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="26" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2685,10 +2746,8 @@
       <c r="G17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2714,10 +2773,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="26" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2743,10 +2800,8 @@
       <c r="G19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="26" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2771,24 +2826,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="8" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="19" t="n"/>
-      <c r="G22" s="19" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="26" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2814,10 +2868,8 @@
       <c r="G23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="26" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2843,10 +2895,8 @@
       <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="26" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2871,6 +2921,8 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="8" t="n"/>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
@@ -2879,17 +2931,19 @@
       </c>
       <c r="D28" s="15">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
+      <c r="F28" s="15">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
@@ -2897,13 +2951,17 @@
         </is>
       </c>
       <c r="B30" s="8" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="25" t="n"/>
       <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
-    </row>
+      <c r="G30" s="25" t="n"/>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
@@ -2922,13 +2980,26 @@
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2937,18 +3008,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2965,10 +3036,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2993,7 +3065,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3008,18 +3080,16 @@
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="25" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -3045,10 +3115,8 @@
       <c r="G6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -3074,10 +3142,8 @@
       <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -3103,10 +3169,8 @@
       <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="26" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -3131,24 +3195,23 @@
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="8" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="26" t="n">
+        <v>5</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -3174,10 +3237,8 @@
       <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="26" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -3203,10 +3264,8 @@
       <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="26" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -3232,10 +3291,8 @@
       <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="26" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -3260,24 +3317,23 @@
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="8" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="26" t="n">
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -3303,10 +3359,8 @@
       <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="26" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -3332,10 +3386,8 @@
       <c r="G19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="26" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -3361,10 +3413,8 @@
       <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="26" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -3389,6 +3439,8 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="8" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -3397,17 +3449,19 @@
       </c>
       <c r="D24" s="15">
         <f>COUNTIF(F5:F22,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>12</v>
-      </c>
-    </row>
+      <c r="F24" s="15">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
@@ -3415,13 +3469,17 @@
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="25" t="n"/>
       <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F26" s="8" t="n"/>
-    </row>
+      <c r="G26" s="25" t="n"/>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
@@ -3440,12 +3498,25 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="F26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
@@ -15,16 +15,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barman" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Jefe de Cocina'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Jefe de Cocina'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Jefe de Cocina'!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sous Chef'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Sous Chef'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Sous Chef'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Jefe de Sala'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jefe de Sala'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jefe de Sala'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Camarero'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Camarero'!$A$1:$G$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Barman'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Barman'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Barman'!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,8 +106,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +150,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3E0"/>
         <bgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -255,6 +280,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,72 +718,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>Tareas por Perfil Profesional — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>▸ Cada pestaña es un perfil profesional diferente</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>▸ Entrega la hoja correspondiente a cada miembro del equipo</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>▸ Son sus responsabilidades diarias — no negociables</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>▸ Estás en 04-tareas-perfiles.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -722,7 +926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -772,7 +976,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -787,517 +991,578 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Verificar que todo el equipo de cocina ha llegado</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Revisar mise en place de todas las partidas</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Probar sazón de todas las elaboraciones</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Aprobar presentación de platos del día</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Comunicar platos del día y 86s a sala</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="38" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Supervisar recepción de mercancía</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>Según entrega</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="8" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="n"/>
+      <c r="B12" s="39" t="n"/>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="25" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Dirigir el pase: control de tiempos y calidad</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Verificar presentación de cada plato antes de salir</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Coordinar entre partidas</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Gestionar devoluciones o reclamaciones de cocina</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="n"/>
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="25" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Evaluar servicio con sous chef: qué mejorar</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Supervisar cierre de todas las partidas</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Planificar carta/especiales del día siguiente</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Revisar pedidos a proveedores</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Actualizar fichas técnicas si hay cambios</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Jefe Cocina</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="38" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D27" s="15">
-        <f>COUNTIF(F5:F25,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F27" s="15">
-        <f>COUNTIF(B5:B25,"?*")</f>
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="A27" s="40" t="n"/>
+      <c r="B27" s="41" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="38" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="n"/>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="38" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="25" t="n"/>
+      <c r="A29" s="40" t="n"/>
+      <c r="B29" s="41" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="38" t="n"/>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D31" s="15">
+        <f>COUNTIFS(B5:B29,"?*",F5:F29,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F31" s="15">
+        <f>COUNTIF(B5:B29,"?*")-COUNTIF(F5:F29,"N/A")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="25" t="n"/>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="25" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
-    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G25">
+  <conditionalFormatting sqref="A5:G29">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1321,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1371,7 +1636,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1386,409 +1651,470 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Organizar equipo de cocina al llegar</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Supervisar FIFO en cámaras</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Preparar lista de pedidos urgentes</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Supervisar mise en place de todas las partidas</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>10:00-11:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Cubrir partida si falta personal</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Si aplica</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="25" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Apoyar en la partida más cargada</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="38" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Cubrir al jefe de cocina en su ausencia</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Si aplica</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Control de calidad de platos en pase</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="n"/>
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="25" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Supervisar limpieza y cierre de cocina</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="38" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Inventario rápido de productos críticos</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Preparar briefing para equipo del día siguiente</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Sous Chef</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n"/>
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="35" t="n"/>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="38" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="n"/>
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="38" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D23" s="15">
-        <f>COUNTIF(F5:F21,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F23" s="15">
-        <f>COUNTIF(B5:B21,"?*")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="40" t="n"/>
+      <c r="B23" s="41" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n"/>
+      <c r="B24" s="41" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="25" t="n"/>
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
     </row>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D27" s="15">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F27" s="15">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F29" s="42" t="n"/>
+      <c r="G29" s="25" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G21">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1812,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1862,7 +2188,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1877,490 +2203,551 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  MAÑANA</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Revisar libro de reservas del día</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Asignar mesas y secciones a camareros</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Verificar montaje completo de sala y terraza</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Briefing pre-servicio: platos del día, alérgenos, VIPs</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Verificar presentación del equipo (uniforme)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="25" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Recibir y acomodar clientes</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="38" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Supervisar tiempos de mesa</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Gestionar reclamaciones en sala</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Coordinar con cocina: tiempos, especiales, alérgenos</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Gestionar walk-ins y lista de espera</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="38" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="n"/>
+      <c r="B18" s="39" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="25" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Revisar reseñas y comentarios del día</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Evaluar servicio con equipo de sala</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Revisar reservas de mañana</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="38" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Supervisar recogida y cierre de sala</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Jefe Sala</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n"/>
+      <c r="B24" s="41" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D26" s="15">
-        <f>COUNTIF(F5:F24,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F26" s="15">
-        <f>COUNTIF(B5:B24,"?*")</f>
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="n"/>
+      <c r="B27" s="41" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="38" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="25" t="n"/>
+      <c r="A28" s="40" t="n"/>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="38" t="n"/>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="15">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F30" s="15">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="25" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G24">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2384,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2434,7 +2821,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2449,544 +2836,605 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Montar mesas de tu sección</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Verificar limpieza de tu sección</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Preparar estación de servicio</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Repasar carta y platos del día</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Asistir al briefing pre-servicio</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="8" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="25" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Dar la bienvenida al cliente con sonrisa</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="38" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Ofrecer carta de bebidas inmediatamente</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Tomar comanda completa (sin volver 2 veces)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="n">
+      <c r="A16" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Preguntar por alérgenos antes de tomar comanda</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="8" t="n"/>
+      <c r="F16" s="37" t="n"/>
+      <c r="G16" s="38" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Servir bebidas en &lt; 3 minutos</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="37" t="n"/>
+      <c r="G17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Retirar platos cuando TODOS los comensales terminen</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="38" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Ofrecer postre y café al finalizar</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Presentar cuenta cuando la pidan (nunca antes)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
-    </row>
-    <row r="21"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="39" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="25" t="n"/>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Desmontar y limpiar mesas de tu sección</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="n">
+      <c r="A24" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Reponer estación de servicio</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>Limpiar menús y cartas</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Camarero</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="8" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="n"/>
+      <c r="B27" s="41" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="37" t="n"/>
+      <c r="G27" s="38" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="15">
-        <f>COUNTIF(F5:F26,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F28" s="15">
-        <f>COUNTIF(B5:B26,"?*")</f>
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="40" t="n"/>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="37" t="n"/>
+      <c r="G28" s="38" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="n"/>
+      <c r="B29" s="41" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="38" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="25" t="n"/>
+      <c r="A30" s="40" t="n"/>
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="37" t="n"/>
+      <c r="G30" s="38" t="n"/>
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D32" s="15">
+        <f>COUNTIFS(B5:B30,"?*",F5:F30,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F32" s="15">
+        <f>COUNTIF(B5:B30,"?*")-COUNTIF(F5:F30,"N/A")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="25" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3010,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3060,7 +3508,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3075,436 +3523,497 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Abrir barra: limpieza, stock, hielo, garnish</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="37" t="n"/>
+      <c r="G6" s="38" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Preparar cafés de prueba (calibrar molinillo)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Revisar vinos por copa: ¿botellas abiertas OK?</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Montar mise en place de cocktails si aplica</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="8" t="n"/>
-    </row>
-    <row r="10"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="n"/>
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="25" t="n"/>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Preparar bebidas en &lt; 2 minutos</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="n">
+      <c r="A13" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Mantener barra limpia y organizada siempre</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="38" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="n">
+      <c r="A14" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Reponer hielo, refrescos y cervezas continuamente</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="n">
+      <c r="A15" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Atender clientes de barra con prioridad</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="8" t="n"/>
-    </row>
-    <row r="16"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="n"/>
+      <c r="B16" s="39" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-      <c r="G17" s="25" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Limpiar barra, fregadero y máquina de café</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="38" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Guardar garnish y productos perecederos</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="F19" s="37" t="n"/>
+      <c r="G19" s="38" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Hacer inventario rápido de cerveza y licores</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="38" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Anotar pedidos necesarios para mañana</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Barman</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="8" t="n"/>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="38" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="n"/>
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="37" t="n"/>
+      <c r="G22" s="38" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n"/>
+      <c r="B23" s="41" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
+      <c r="F23" s="37" t="n"/>
+      <c r="G23" s="38" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D24" s="15">
-        <f>COUNTIF(F5:F22,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F24" s="15">
-        <f>COUNTIF(B5:B22,"?*")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="A24" s="40" t="n"/>
+      <c r="B24" s="41" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="37" t="n"/>
+      <c r="G24" s="38" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="35" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="37" t="n"/>
+      <c r="G25" s="38" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="25" t="n"/>
+      <c r="A26" s="40" t="n"/>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="38" t="n"/>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="15">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28" s="15">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="25" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G22">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas/04-tareas-perfiles.xlsx
@@ -793,6 +793,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="28" t="inlineStr">
         <is>
@@ -800,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="29" t="inlineStr">
         <is>
@@ -814,6 +816,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="18" customHeight="1">
       <c r="B21" s="28" t="inlineStr">
         <is>
@@ -821,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="29" t="inlineStr">
         <is>
@@ -835,6 +839,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="28" t="inlineStr">
         <is>
@@ -842,10 +847,11 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="27"/>
+    <row r="28" ht="16" customHeight="1">
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -863,10 +869,10 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="48" customHeight="1">
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -877,6 +883,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="28" t="inlineStr">
         <is>
@@ -884,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="35" customHeight="1">
       <c r="B36" s="28" t="inlineStr">
         <is>
@@ -898,6 +906,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="28" t="inlineStr">
         <is>
@@ -1562,7 +1571,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2114,7 +2123,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2732,8 +2741,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="A2:G2"/>
@@ -2747,7 +2756,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3424,8 +3433,8 @@
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G30">
@@ -3434,7 +3443,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4013,7 +4022,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F12 F13 F14 F15 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
